--- a/outputs/2. City of York Council (Final).xlsx
+++ b/outputs/2. City of York Council (Final).xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U46"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,61 +489,16 @@
           <t>Risk Priority (post-mitigation)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Schema Alignment Log</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Risk ID (Reasoning)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Risk Description (Reasoning)</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Project Stage (Reasoning)</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Project Category (Reasoning)</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Risk Owner (Reasoning)</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Likelihood (Reasoning)</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Impact (Reasoning)</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Mitigating Action (Reasoning)</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Failure to discharge planning and listed building conditions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -563,86 +518,41 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Design team and contractor to collate initial pack of information for discharge of conditions</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Planning conditions impact on budget</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -662,11 +572,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Extent of conditions known and to be reviewed and managed</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
@@ -677,71 +587,26 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Electricity provider works delayed or non-conforming</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -761,86 +626,41 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Orders for the electrical services have been placed by CYC direct</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Building Control Sign Off delay due to lack of resources</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -860,86 +680,41 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Continue liaison with the Building Control Officer</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Impact of boat companies (City Cruises) on delivery and site servicing strategy.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -959,86 +734,41 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Legal agreements are in place.</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Party wall negotiations &amp; construction access</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1058,14 +788,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Appoint party wall surveyor and progress discussions with neighbours</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1073,71 +803,26 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Failure to secure market interest for restaurant tenant</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1157,14 +842,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Early engagement of agent for potential lettings. Sufficient expressions of interest</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1172,71 +857,26 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Increased construction costs due to exchange rate fluctuations on materials and the impact of international markets following political decisions.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1256,7 +896,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Tender prices received and under review. Risk shall remain prominent where budget costs / provisional sums are included.</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1271,71 +911,26 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Sub-contractor insolvency</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1355,11 +950,11 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Contractor financial checks and vetting of subcontractors</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
         <v>5</v>
@@ -1370,71 +965,26 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Surveys required to determine ground conditions/ contamination</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1454,86 +1004,41 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>GI survey undertaken, information obtained. Contamination results received. - Desk study provided by Arup</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Identification of active movement</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1553,86 +1058,41 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Ongoing monitoring by ARUP and monitoring specification included within contract documents</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Unidentified archaeology</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1652,86 +1112,41 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Evaluation of site undertaken</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Additional surveys required</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1751,86 +1166,41 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Undertake outstanding surveys</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Unrealistic programme submitted by contractor</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1850,86 +1220,41 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Market tested</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Programme delays due to flood levels impacting construction</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1949,86 +1274,41 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Review historic flood data and issue to Contractor. Contingency plan to be developed</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Delay to design programme</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2048,7 +1328,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Implementation of IRS schedules design deliverables and clear responsibility for design</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2063,71 +1343,26 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Underpinning, piling and crack repairs to be considered. May resolve existing cracks and movement of the tower but other cracks may appear elsewhere that will require repairing.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2147,14 +1382,14 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Detailed dilapidations surveys, crack monitors</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>5</v>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2162,71 +1397,26 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Discovering structural unknowns</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2246,14 +1436,14 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Undertake surveys early to determine unknowns. Allow suitable contingency for remediation. Biggest concerns being the tower underpinning and South Range.</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2261,71 +1451,26 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Undetected services not identified on surveys and drawings</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2345,86 +1490,41 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Utilities surveys maps obtained and plotted on SGA drawings. Careful excavation / groundworks when on site</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
         <v>5</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>River source heat pump license approval by the Environment Agency; Refused</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2444,86 +1544,41 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Provisional consent obtained; continued dialogue required</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Sourcing stone for remediation works. Quarry that stone exists from is closed. Impacts programme, and different stone requires further approval from Historic England and the planning authority.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2543,11 +1598,11 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Investigate other quarries which supply the stone. Liaise with Historic England and the planning authority to have an alternative approved.</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H22" t="n">
         <v>5</v>
@@ -2558,71 +1613,26 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Structural damage and the repairs required to the tower</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2642,14 +1652,14 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Bullivants / Arup design and Vinci temporary works design to be reviewed in detail to mitigate any consequential delay. Building monitoring systems and locations to be agreed.</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2657,71 +1667,26 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Outstanding defects remaining unresolved, leaving CYC with legacy issues and building defects which need resolving, impacting tenant occupation and satisfaction.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2741,86 +1706,41 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Ability to resolve within the building contract. Use of retention.</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H24" t="n">
         <v>5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>3</v>
       </c>
       <c r="K24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Costs exceeds allocated budget (Non Construction costs). Particular risks surrounding consultant fees, furniture / fit out works etc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2840,11 +1760,11 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Review non construction costs prior to contract award and during construction</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H25" t="n">
         <v>5</v>
@@ -2855,71 +1775,26 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Incorrect estimation design errors and ambiguities</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2939,7 +1814,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Risk sits with CYC except CDP items</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -2954,71 +1829,26 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Availability of specialist labour / equipment</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3038,7 +1868,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Dialogue with main contractor &amp; supply chain</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3053,71 +1883,26 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Poor co-ordination with design team interfaces (contractor design portions)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3137,86 +1922,41 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>CDP requirements have reduced from initial intent - Regular meetings to be held with Vinci and Design Team to discuss CDP interfaces.</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H28" t="n">
         <v>5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>3</v>
       </c>
       <c r="K28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Rights of Light</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3236,86 +1976,41 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Title report does not identify any issues</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Poor contractor performance during construction</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3335,14 +2030,14 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Contract to be signed to protect client - performance bonds to be obtained.</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H30" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3353,68 +2048,23 @@
         <v>3</v>
       </c>
       <c r="K30" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Unknown South Range structures. Risk of discovering old basement causing issues with piling proposals.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3432,13 +2082,9 @@
           <t>Structural Engineer</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Monitor and evaluate.</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H31" t="n">
         <v>5</v>
@@ -3449,71 +2095,26 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Insufficient design detail from specialist CDP packages</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3533,86 +2134,41 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Regular design reviews and interface management</t>
         </is>
       </c>
       <c r="G32" t="n">
         <v>5</v>
       </c>
       <c r="H32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Satisfying EA requirements. Incident occurring which stops the work and action required to resolve the issue. EA Prohibition.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3632,86 +2188,41 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Waste management and compliance with the EA to ensure no environmental hazards</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Delay in design programme due to tenant/operator requirements</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3731,7 +2242,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Recovery of cost / time included within the Agreements for Lease should late or significant changes be made</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -3746,71 +2257,26 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Design changes (including client changes/ variations / EOT &amp; loss &amp; expense claims) and unforeseen items</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3830,86 +2296,41 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Traditional contract — risk with CYC; secure adequate contingency</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H35" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K35" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Weather delays</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3929,11 +2350,11 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Contractor to provide impact and allowances via contract</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H36" t="n">
         <v>5</v>
@@ -3944,71 +2365,26 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Underpinning/ crack repairs by third parties</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4028,14 +2404,14 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Detailed dilapidations surveys, crack monitors</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -4046,68 +2422,23 @@
         <v>3</v>
       </c>
       <c r="K37" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Ground conditions - Borehole survey depth insufficient. Proposed piling designs impacted by this and require altering - Time &amp; Cost impact.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4127,7 +2458,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Additional bore hole surveys undertaken, no foundations / obstructions found albeit at relatively shallow depth. (near tower) Bullivants / Arup to review surveys and confirm they are happy with findings. Vinci to design piling to new structures and confirm site information held is adequate.</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4152,61 +2483,16 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Instability to boundary wall following demolition</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4226,86 +2512,41 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Assessment of wall structure required - Scope of works to be determined</t>
         </is>
       </c>
       <c r="G39" t="n">
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Clashes between the existing building foundations and proposed drainage network. No information is available for the existing buildings therefore it has not been possible to co-ordinate the height of drainage to pass above/ under the existing foundation as required.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4325,86 +2566,41 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Trial holes could be undertaken to better understand the existing foundations. Drainage has been designed conservatively to allow for a level of contingency in the design if foundations impact drainage runs.</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Potential drainage clash with proposed lift shaft pits</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4424,86 +2620,41 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Trial hole dug in the location and appears to be clear - risk to be reviewed again once demolition of north annex is complete.</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
         <v>5</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Billing omissions or inaccuracies in BoQ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4523,14 +2674,14 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>T&amp;T have carried out reviews of the BoQ</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H42" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -4538,71 +2689,26 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K42" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Additional works not covered by contract documents. Arising from opening up works / scope and extent of works greater than assumed etc.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4622,86 +2728,41 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Detailed change management process to be followed.</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H43" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K43" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Ongoing movement in the south range, given the removal of underpinning from the scheme</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4721,86 +2782,41 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Monitoring during works</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J44" t="n">
         <v>3</v>
       </c>
       <c r="K44" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>87</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Design change due to level of development and coordination at the point of tender, for items such as North Annex chimney, retaining walls and stairs, and movement joints to existing structures.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4820,86 +2836,41 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Coordination to be managed by design team as a priority - Design changes to retaining concrete wall has been instructed by CYC and should be underway by design team.</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J45" t="n">
         <v>3</v>
       </c>
       <c r="K45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Council chamber cooling to be approved</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4919,74 +2890,29 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Design team to coordinate with planning / conservation</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H46" t="n">
         <v>5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J46" t="n">
         <v>3</v>
       </c>
       <c r="K46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
